--- a/调整后问卷_SEM模型适配版.xlsx
+++ b/调整后问卷_SEM模型适配版.xlsx
@@ -656,6 +656,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -684,6 +685,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -726,6 +728,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
@@ -768,6 +771,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
@@ -810,6 +814,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
@@ -852,6 +857,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
@@ -901,6 +907,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
@@ -915,6 +922,7 @@
         </is>
       </c>
     </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
@@ -1055,6 +1063,7 @@
         </is>
       </c>
     </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
@@ -1195,6 +1204,7 @@
         </is>
       </c>
     </row>
+    <row r="60"/>
     <row r="61">
       <c r="A61" s="13" t="inlineStr">
         <is>
@@ -1335,6 +1345,7 @@
         </is>
       </c>
     </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
@@ -1475,6 +1486,7 @@
         </is>
       </c>
     </row>
+    <row r="72"/>
     <row r="73">
       <c r="A73" s="13" t="inlineStr">
         <is>
@@ -1615,6 +1627,7 @@
         </is>
       </c>
     </row>
+    <row r="78"/>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
@@ -1662,7 +1675,7 @@
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>NE1. 烟台自然环境有利于特色电商产品的培育与生产</t>
+          <t>EN1. 烟台自然环境有利于特色电商产品的培育与生产</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
@@ -1694,7 +1707,7 @@
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>NE2. 本地特色资源能为集群电商发展提供核心竞争力</t>
+          <t>EN2. 本地特色资源能为集群电商发展提供核心竞争力</t>
         </is>
       </c>
       <c r="B82" s="12" t="inlineStr">
@@ -1726,7 +1739,7 @@
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>NE3. 资源整合利用效率能支撑电商产业规模化发展</t>
+          <t>EN3. 资源整合利用效率能支撑电商产业规模化发展</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
@@ -1755,6 +1768,7 @@
         </is>
       </c>
     </row>
+    <row r="84"/>
     <row r="85">
       <c r="A85" s="14" t="inlineStr">
         <is>
@@ -1902,6 +1916,7 @@
         </is>
       </c>
     </row>
+    <row r="91"/>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
@@ -1923,6 +1938,7 @@
         </is>
       </c>
     </row>
+    <row r="95"/>
     <row r="96">
       <c r="A96" s="21" t="inlineStr">
         <is>
@@ -1947,7 +1963,7 @@
     <row r="99" ht="45" customHeight="1">
       <c r="A99" s="22" t="inlineStr">
         <is>
-          <t>3. 【保留】第二部分维度一至维度六（GP1-GP3, TS1-TS3, IF1-IF3, TI1-TI3, DS1-DS3, NE1-NE3）：18道李克特五级量表题，与原问卷完全一致。</t>
+          <t>3. 【保留】第二部分维度一至维度六（GP1-GP3, TS1-TS3, IF1-IF3, TI1-TI3, DS1-DS3, EN1-EN3）：18道李克特五级量表题，与原问卷完全一致。</t>
         </is>
       </c>
     </row>
@@ -1988,10 +2004,11 @@
     <row r="106" ht="45" customHeight="1">
       <c r="A106" s="22" t="inlineStr">
         <is>
-          <t>SEM模型使用的变量：GP(3题) + TS(3题) + IF(3题) + TI(3题) + DS(3题) + NE(3题) → CDL(3题)，共21个观测指标。</t>
-        </is>
-      </c>
-    </row>
+          <t>SEM模型使用的变量：GP(3题) + TS(3题) + IF(3题) + TI(3题) + DS(3题) + EN(3题) → CDL(3题)，共21个观测指标。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107"/>
     <row r="108">
       <c r="A108" s="23" t="inlineStr">
         <is>
@@ -2194,7 +2211,7 @@
     <row r="115">
       <c r="A115" s="25" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="B115" s="25" t="inlineStr">
@@ -2209,7 +2226,7 @@
       </c>
       <c r="D115" s="25" t="inlineStr">
         <is>
-          <t>NE1, NE2, NE3</t>
+          <t>EN1, EN2, EN3</t>
         </is>
       </c>
       <c r="E115" s="25" t="inlineStr">
@@ -2266,12 +2283,12 @@
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A101:F101"/>
     <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A104:F104"/>
     <mergeCell ref="A86:F86"/>
-    <mergeCell ref="A101:F101"/>
-    <mergeCell ref="A104:F104"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="A47:F47"/>
